--- a/cap741-data.xlsx
+++ b/cap741-data.xlsx
@@ -402,20 +402,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L21"/>
-  <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="28.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="40.83203125" customWidth="1"/>
-    <col min="8" max="8" width="70.83203125" customWidth="1"/>
-    <col min="9" max="9" width="70.83203125" customWidth="1"/>
-    <col min="10" max="10" width="24.83203125" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" customWidth="1"/>
-    <col min="12" max="12" width="22.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -617,10 +603,10 @@
         <v>G-ZBLB</v>
       </c>
       <c r="C6" t="str">
-        <v>99-hi</v>
+        <v>99</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>hi</v>
       </c>
       <c r="E6" t="str">
         <v>14/02/2023</v>
@@ -883,10 +869,10 @@
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>99-hi</v>
+        <v>99</v>
       </c>
       <c r="D13" t="str">
-        <v/>
+        <v>hi</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -921,10 +907,10 @@
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>99-hi</v>
+        <v>99</v>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>hi</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -959,10 +945,10 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>99-hi</v>
+        <v>99</v>
       </c>
       <c r="D15" t="str">
-        <v/>
+        <v>hi</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -997,10 +983,10 @@
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>99-hi</v>
+        <v>99</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>hi</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1035,10 +1021,10 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>99-hi</v>
+        <v>99</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>hi</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1073,10 +1059,10 @@
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>99-hi</v>
+        <v>99</v>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>hi</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1227,11 +1213,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C88"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="38.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2210,11 +2191,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B74"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="36.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:B73"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2800,17 +2777,9 @@
         <v>Propulsion Augmentation</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>99-hi</v>
-      </c>
-      <c r="B74" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B74"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B73"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2818,14 +2787,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F29"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3417,10 +3378,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B4"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/cap741-data.xlsx
+++ b/cap741-data.xlsx
@@ -1173,10 +1173,10 @@
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D21" t="str">
-        <v>Navigation</v>
+        <v>General Description</v>
       </c>
       <c r="E21" t="str">
         <v/>

--- a/cap741-data.xlsx
+++ b/cap741-data.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1167,16 +1167,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Airbus A380-800 - RR Trent 900</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
       <c r="B21" t="str">
-        <v/>
+        <v>G-STBH</v>
       </c>
       <c r="C21" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="D21" t="str">
-        <v>General Description</v>
+        <v/>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1203,9 +1203,275 @@
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+      <c r="B22" t="str">
+        <v>G-STBH</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>ddddddddddddddddddddd</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v/>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>vsdvvz</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>ff</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Airbus A380-800 - RR Trent 900</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v>34</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Navigation</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v/>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v/>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v/>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L28"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/cap741-data.xlsx
+++ b/cap741-data.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -977,16 +977,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Boeing 787-10 - RR Trent 1000</v>
+        <v>Airbus A380-800 - RR Trent 900</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="D16" t="str">
-        <v>hi</v>
+        <v>Navigation</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -995,13 +995,13 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>ss</v>
       </c>
       <c r="H16" t="str">
         <v>h</v>
       </c>
       <c r="I16" t="str">
-        <v>h</v>
+        <v>hhhhhhhhhhhhhhhh</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1015,16 +1015,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Boeing 787-10 - RR Trent 1000</v>
+        <v>Airbus A380-800 - RR Trent 900</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="D17" t="str">
-        <v>hi</v>
+        <v>Navigation</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1039,7 +1039,7 @@
         <v>h</v>
       </c>
       <c r="I17" t="str">
-        <v>h</v>
+        <v>hhhhhhhhhhh</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1053,16 +1053,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Boeing 787-10 - RR Trent 1000</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>G-STBH</v>
       </c>
       <c r="C18" t="str">
-        <v>99</v>
+        <v/>
       </c>
       <c r="D18" t="str">
-        <v>hi</v>
+        <v/>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1074,10 +1074,10 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>h</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>h</v>
+        <v>jjjjjj</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1091,16 +1091,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Airbus A380-800 - RR Trent 900</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>G-STBH</v>
       </c>
       <c r="C19" t="str">
-        <v>34</v>
+        <v/>
       </c>
       <c r="D19" t="str">
-        <v>Navigation</v>
+        <v/>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1109,13 +1109,13 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>ss</v>
+        <v/>
       </c>
       <c r="H19" t="str">
-        <v>h</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v>hhhhhhhhhhhhhhhh</v>
+        <v>ddddddddddddddddddddd</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1124,354 +1124,12 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Airbus A380-800 - RR Trent 900</v>
-      </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v>34</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Navigation</v>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
-        <v>h</v>
-      </c>
-      <c r="I20" t="str">
-        <v>hhhhhhhhhhh</v>
-      </c>
-      <c r="J20" t="str">
-        <v/>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Boeing 777-300ER - GE90</v>
-      </c>
-      <c r="B21" t="str">
-        <v>G-STBH</v>
-      </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v>jjjjjj</v>
-      </c>
-      <c r="J21" t="str">
-        <v/>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Boeing 777-300ER - GE90</v>
-      </c>
-      <c r="B22" t="str">
-        <v>G-STBH</v>
-      </c>
-      <c r="C22" t="str">
-        <v/>
-      </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
-      <c r="E22" t="str">
-        <v/>
-      </c>
-      <c r="F22" t="str">
-        <v/>
-      </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v>ddddddddddddddddddddd</v>
-      </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v/>
-      </c>
-      <c r="B23" t="str">
-        <v/>
-      </c>
-      <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="D23" t="str">
-        <v/>
-      </c>
-      <c r="E23" t="str">
-        <v/>
-      </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v>vsdvvz</v>
-      </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v/>
-      </c>
-      <c r="B24" t="str">
-        <v/>
-      </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <v/>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-      <c r="F24" t="str">
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v>ff</v>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Airbus A380-800 - RR Trent 900</v>
-      </c>
-      <c r="B25" t="str">
-        <v/>
-      </c>
-      <c r="C25" t="str">
-        <v>34</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Navigation</v>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v/>
-      </c>
-      <c r="B26" t="str">
-        <v/>
-      </c>
-      <c r="C26" t="str">
-        <v/>
-      </c>
-      <c r="D26" t="str">
-        <v/>
-      </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
-      <c r="F26" t="str">
-        <v/>
-      </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v/>
-      </c>
-      <c r="B27" t="str">
-        <v/>
-      </c>
-      <c r="C27" t="str">
-        <v/>
-      </c>
-      <c r="D27" t="str">
-        <v/>
-      </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
-      <c r="F27" t="str">
-        <v/>
-      </c>
-      <c r="G27" t="str">
-        <v/>
-      </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
-      <c r="J27" t="str">
-        <v/>
-      </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v/>
-      </c>
-      <c r="B28" t="str">
-        <v/>
-      </c>
-      <c r="C28" t="str">
-        <v/>
-      </c>
-      <c r="D28" t="str">
-        <v/>
-      </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
-      <c r="F28" t="str">
-        <v/>
-      </c>
-      <c r="G28" t="str">
-        <v/>
-      </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
-      <c r="J28" t="str">
-        <v/>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L19"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/cap741-data.xlsx
+++ b/cap741-data.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L376"/>
+  <dimension ref="A1:L378"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14772,9 +14772,85 @@
         <v/>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>Airbus A350-1000 - RR Trent XWB-97</v>
+      </c>
+      <c r="B377" t="str">
+        <v/>
+      </c>
+      <c r="C377" t="str">
+        <v>5</v>
+      </c>
+      <c r="D377" t="str">
+        <v>Time Limits/Maintenance Checks</v>
+      </c>
+      <c r="E377" t="str">
+        <v/>
+      </c>
+      <c r="F377" t="str">
+        <v/>
+      </c>
+      <c r="G377" t="str">
+        <v/>
+      </c>
+      <c r="H377" t="str">
+        <v/>
+      </c>
+      <c r="I377" t="str">
+        <v/>
+      </c>
+      <c r="J377" t="str">
+        <v/>
+      </c>
+      <c r="K377" t="str">
+        <v/>
+      </c>
+      <c r="L377" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>Airbus A350-1000 - RR Trent XWB-97</v>
+      </c>
+      <c r="B378" t="str">
+        <v/>
+      </c>
+      <c r="C378" t="str">
+        <v>5</v>
+      </c>
+      <c r="D378" t="str">
+        <v>Time Limits/Maintenance Checks</v>
+      </c>
+      <c r="E378" t="str">
+        <v/>
+      </c>
+      <c r="F378" t="str">
+        <v/>
+      </c>
+      <c r="G378" t="str">
+        <v/>
+      </c>
+      <c r="H378" t="str">
+        <v/>
+      </c>
+      <c r="I378" t="str">
+        <v/>
+      </c>
+      <c r="J378" t="str">
+        <v/>
+      </c>
+      <c r="K378" t="str">
+        <v/>
+      </c>
+      <c r="L378" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L376"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L378"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15022,7 +15098,7 @@
         <v>G-STBC</v>
       </c>
       <c r="C22" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-300 - GE90</v>
       </c>
     </row>
     <row r="23">
@@ -15033,7 +15109,7 @@
         <v>G-STBE</v>
       </c>
       <c r="C23" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-300 - GE90</v>
       </c>
     </row>
     <row r="24">
@@ -15044,7 +15120,7 @@
         <v>G-STBF</v>
       </c>
       <c r="C24" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-300 - GE90</v>
       </c>
     </row>
     <row r="25">
@@ -15055,7 +15131,7 @@
         <v>G-STBG</v>
       </c>
       <c r="C25" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-300 - GE90</v>
       </c>
     </row>
     <row r="26">
@@ -15066,7 +15142,7 @@
         <v>G-STBH</v>
       </c>
       <c r="C26" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-300 - GE90</v>
       </c>
     </row>
     <row r="27">
@@ -15077,7 +15153,7 @@
         <v>G-STBK</v>
       </c>
       <c r="C27" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-300 - GE90</v>
       </c>
     </row>
     <row r="28">
@@ -15088,7 +15164,7 @@
         <v>G-STBL</v>
       </c>
       <c r="C28" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-300 - GE90</v>
       </c>
     </row>
     <row r="29">
@@ -15099,7 +15175,7 @@
         <v>G-STBM</v>
       </c>
       <c r="C29" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-300 - GE90</v>
       </c>
     </row>
     <row r="30">
@@ -15110,7 +15186,7 @@
         <v>G-STBN</v>
       </c>
       <c r="C30" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-300 - GE90</v>
       </c>
     </row>
     <row r="31">
@@ -15121,7 +15197,7 @@
         <v>G-STBO</v>
       </c>
       <c r="C31" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-300 - GE90</v>
       </c>
     </row>
     <row r="32">
@@ -15132,7 +15208,7 @@
         <v>G-VIIA</v>
       </c>
       <c r="C32" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-200 - GE90</v>
       </c>
     </row>
     <row r="33">
@@ -15143,7 +15219,7 @@
         <v>G-VIIB</v>
       </c>
       <c r="C33" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-200 - GE90</v>
       </c>
     </row>
     <row r="34">
@@ -15154,7 +15230,7 @@
         <v>G-VIIC</v>
       </c>
       <c r="C34" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-200 - GE90</v>
       </c>
     </row>
     <row r="35">
@@ -15165,7 +15241,7 @@
         <v>G-VIIE</v>
       </c>
       <c r="C35" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-200 - GE90</v>
       </c>
     </row>
     <row r="36">
@@ -15176,7 +15252,7 @@
         <v>G-VIIF</v>
       </c>
       <c r="C36" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-200 - GE90</v>
       </c>
     </row>
     <row r="37">
@@ -15187,7 +15263,7 @@
         <v>G-VIIG</v>
       </c>
       <c r="C37" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-200 - GE90</v>
       </c>
     </row>
     <row r="38">
@@ -15198,7 +15274,7 @@
         <v>G-VIIH</v>
       </c>
       <c r="C38" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-200 - GE90</v>
       </c>
     </row>
     <row r="39">
@@ -15209,7 +15285,7 @@
         <v>G-VIIJ</v>
       </c>
       <c r="C39" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-200 - GE90</v>
       </c>
     </row>
     <row r="40">
@@ -15220,7 +15296,7 @@
         <v>G-VIIK</v>
       </c>
       <c r="C40" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-200 - GE90</v>
       </c>
     </row>
     <row r="41">
@@ -15231,7 +15307,7 @@
         <v>G-VIIL</v>
       </c>
       <c r="C41" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-200 - GE90</v>
       </c>
     </row>
     <row r="42">
@@ -15242,7 +15318,7 @@
         <v>G-VIIN</v>
       </c>
       <c r="C42" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-200 - GE90</v>
       </c>
     </row>
     <row r="43">
@@ -15253,7 +15329,7 @@
         <v>G-VIIP</v>
       </c>
       <c r="C43" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-300 - GE90</v>
       </c>
     </row>
     <row r="44">
@@ -15264,7 +15340,7 @@
         <v>G-VIIS</v>
       </c>
       <c r="C44" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-300 - GE90</v>
       </c>
     </row>
     <row r="45">
@@ -15275,7 +15351,7 @@
         <v>G-VIIV</v>
       </c>
       <c r="C45" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-300 - GE90</v>
       </c>
     </row>
     <row r="46">
@@ -15286,7 +15362,7 @@
         <v>G-VIIW</v>
       </c>
       <c r="C46" t="str">
-        <v>Boeing 777-300ER - GE90</v>
+        <v>Boeing 777-300 - GE90</v>
       </c>
     </row>
     <row r="47">
@@ -15297,7 +15373,7 @@
         <v>G-YMMB</v>
       </c>
       <c r="C47" t="str">
-        <v>Boeing 777-200ER - RR Trent 800</v>
+        <v>Boeing 777-200 - RR Trent 800</v>
       </c>
     </row>
     <row r="48">
@@ -15308,7 +15384,7 @@
         <v>G-YMMF</v>
       </c>
       <c r="C48" t="str">
-        <v>Boeing 777-200ER - RR Trent 800</v>
+        <v>Boeing 777-200 - RR Trent 800</v>
       </c>
     </row>
     <row r="49">
@@ -15319,7 +15395,7 @@
         <v>G-YMMG</v>
       </c>
       <c r="C49" t="str">
-        <v>Boeing 777-200ER - RR Trent 800</v>
+        <v>Boeing 777-200 - RR Trent 800</v>
       </c>
     </row>
     <row r="50">
@@ -15330,7 +15406,7 @@
         <v>G-YMMI</v>
       </c>
       <c r="C50" t="str">
-        <v>Boeing 777-200ER - RR Trent 800</v>
+        <v>Boeing 777-200 - RR Trent 800</v>
       </c>
     </row>
     <row r="51">
@@ -15341,7 +15417,7 @@
         <v>G-YMMJ</v>
       </c>
       <c r="C51" t="str">
-        <v>Boeing 777-200ER - RR Trent 800</v>
+        <v>Boeing 777-200 - RR Trent 800</v>
       </c>
     </row>
     <row r="52">
@@ -15352,7 +15428,7 @@
         <v>G-YMMK</v>
       </c>
       <c r="C52" t="str">
-        <v>Boeing 777-200ER - RR Trent 800</v>
+        <v>Boeing 777-200 - RR Trent 800</v>
       </c>
     </row>
     <row r="53">
@@ -15363,7 +15439,7 @@
         <v>G-YMMP</v>
       </c>
       <c r="C53" t="str">
-        <v>Boeing 777-200ER - RR Trent 800</v>
+        <v>Boeing 777-200 - RR Trent 800</v>
       </c>
     </row>
     <row r="54">
@@ -15374,7 +15450,7 @@
         <v>G-YMMT</v>
       </c>
       <c r="C54" t="str">
-        <v>Boeing 777-200ER - RR Trent 800</v>
+        <v>Boeing 777-200 - RR Trent 800</v>
       </c>
     </row>
     <row r="55">
@@ -15385,7 +15461,7 @@
         <v>G-YMMU</v>
       </c>
       <c r="C55" t="str">
-        <v>Boeing 777-200ER - RR Trent 800</v>
+        <v>Boeing 777-200 - RR Trent 800</v>
       </c>
     </row>
     <row r="56">

--- a/cap741-data.xlsx
+++ b/cap741-data.xlsx
@@ -9749,7 +9749,7 @@
         <v>PERIODIC GROUND CHECK AT 7-DAY INTERVALS CARRIED OUT IAW DIR 10317077 PT 000 VERS 01. SEE SAP REVISION 01315524 DCN 001, 002 AND 003 FOR DETAILS</v>
       </c>
       <c r="I243" t="str">
-        <v>Assisted with PERIODIC GROUND CHECK AT 7-DAY INTERVALS CARRIED OUT IAW DIR 10317077 PT 000 VERS 01. SEE SAP REVISION 01315524 DCN 001, 002 AND 003 FOR DETAILS for Action Maintenance Notification 40152456 - D7 NOTIFICATION, WBC STORAGE 7 DAY PE- D7 NOTIFICATION, W...</v>
+        <v>Assisted with PERIODIC GROUND CHECK AT 7-DAY INTERVALS CARRIED OUT IAW DIR 10317077 PT 000 VERS 01. SEE SAP REVISION 01315524 DCN 001, 002 AND 003 FOR DETAILS for Action Maintenance Notification 40152456 - D7 NOTIFICATION, WBC STORAGE 7 DAY PE- D7 NOTIFICATION, W...c</v>
       </c>
       <c r="J243" t="str">
         <v>Kevin Cosgrave</v>

--- a/cap741-data.xlsx
+++ b/cap741-data.xlsx
@@ -1,18 +1,34 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
-  <sheets>
-    <sheet name="Logbook" sheetId="1" r:id="rId1"/>
-    <sheet name="Aircraft" sheetId="2" r:id="rId2"/>
-    <sheet name="Chapters" sheetId="3" r:id="rId3"/>
-    <sheet name="Supervisors" sheetId="4" r:id="rId4"/>
-    <sheet name="Info" sheetId="5" r:id="rId5"/>
-  </sheets>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>SheetJS</Application>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Worksheets</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>5</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="5" baseType="lpstr">
+      <vt:lpstr>Logbook</vt:lpstr>
+      <vt:lpstr>Aircraft</vt:lpstr>
+      <vt:lpstr>Chapters</vt:lpstr>
+      <vt:lpstr>Supervisors</vt:lpstr>
+      <vt:lpstr>Info</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+</Properties>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance"/>
+</file>
+
+<file path=xl\metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
@@ -34,7 +50,7 @@
 </metadata>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
@@ -79,7 +95,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -399,7 +415,20 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <sheets>
+    <sheet name="Logbook" sheetId="1" r:id="rId1"/>
+    <sheet name="Aircraft" sheetId="2" r:id="rId2"/>
+    <sheet name="Chapters" sheetId="3" r:id="rId3"/>
+    <sheet name="Supervisors" sheetId="4" r:id="rId4"/>
+    <sheet name="Info" sheetId="5" r:id="rId5"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L376"/>
   <sheetData>
@@ -14822,7 +14851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C88"/>
   <sheetData>
@@ -15065,7 +15094,7 @@
         <v>G-STBC</v>
       </c>
       <c r="C22" t="str">
-        <v>Boeing 777-300 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="23">
@@ -15076,7 +15105,7 @@
         <v>G-STBE</v>
       </c>
       <c r="C23" t="str">
-        <v>Boeing 777-300 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="24">
@@ -15087,7 +15116,7 @@
         <v>G-STBF</v>
       </c>
       <c r="C24" t="str">
-        <v>Boeing 777-300 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="25">
@@ -15098,7 +15127,7 @@
         <v>G-STBG</v>
       </c>
       <c r="C25" t="str">
-        <v>Boeing 777-300 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="26">
@@ -15109,7 +15138,7 @@
         <v>G-STBH</v>
       </c>
       <c r="C26" t="str">
-        <v>Boeing 777-300 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="27">
@@ -15120,7 +15149,7 @@
         <v>G-STBK</v>
       </c>
       <c r="C27" t="str">
-        <v>Boeing 777-300 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="28">
@@ -15131,7 +15160,7 @@
         <v>G-STBL</v>
       </c>
       <c r="C28" t="str">
-        <v>Boeing 777-300 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="29">
@@ -15142,7 +15171,7 @@
         <v>G-STBM</v>
       </c>
       <c r="C29" t="str">
-        <v>Boeing 777-300 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="30">
@@ -15153,7 +15182,7 @@
         <v>G-STBN</v>
       </c>
       <c r="C30" t="str">
-        <v>Boeing 777-300 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="31">
@@ -15164,7 +15193,7 @@
         <v>G-STBO</v>
       </c>
       <c r="C31" t="str">
-        <v>Boeing 777-300 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="32">
@@ -15175,7 +15204,7 @@
         <v>G-VIIA</v>
       </c>
       <c r="C32" t="str">
-        <v>Boeing 777-200 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="33">
@@ -15186,7 +15215,7 @@
         <v>G-VIIB</v>
       </c>
       <c r="C33" t="str">
-        <v>Boeing 777-200 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="34">
@@ -15197,7 +15226,7 @@
         <v>G-VIIC</v>
       </c>
       <c r="C34" t="str">
-        <v>Boeing 777-200 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="35">
@@ -15208,7 +15237,7 @@
         <v>G-VIIE</v>
       </c>
       <c r="C35" t="str">
-        <v>Boeing 777-200 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="36">
@@ -15219,7 +15248,7 @@
         <v>G-VIIF</v>
       </c>
       <c r="C36" t="str">
-        <v>Boeing 777-200 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="37">
@@ -15230,7 +15259,7 @@
         <v>G-VIIG</v>
       </c>
       <c r="C37" t="str">
-        <v>Boeing 777-200 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="38">
@@ -15241,7 +15270,7 @@
         <v>G-VIIH</v>
       </c>
       <c r="C38" t="str">
-        <v>Boeing 777-200 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="39">
@@ -15252,7 +15281,7 @@
         <v>G-VIIJ</v>
       </c>
       <c r="C39" t="str">
-        <v>Boeing 777-200 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="40">
@@ -15263,7 +15292,7 @@
         <v>G-VIIK</v>
       </c>
       <c r="C40" t="str">
-        <v>Boeing 777-200 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="41">
@@ -15274,7 +15303,7 @@
         <v>G-VIIL</v>
       </c>
       <c r="C41" t="str">
-        <v>Boeing 777-200 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="42">
@@ -15285,7 +15314,7 @@
         <v>G-VIIN</v>
       </c>
       <c r="C42" t="str">
-        <v>Boeing 777-200 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="43">
@@ -15296,7 +15325,7 @@
         <v>G-VIIP</v>
       </c>
       <c r="C43" t="str">
-        <v>Boeing 777-300 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="44">
@@ -15307,7 +15336,7 @@
         <v>G-VIIS</v>
       </c>
       <c r="C44" t="str">
-        <v>Boeing 777-300 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="45">
@@ -15318,7 +15347,7 @@
         <v>G-VIIV</v>
       </c>
       <c r="C45" t="str">
-        <v>Boeing 777-300 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="46">
@@ -15329,7 +15358,7 @@
         <v>G-VIIW</v>
       </c>
       <c r="C46" t="str">
-        <v>Boeing 777-300 - GE90</v>
+        <v>Boeing 777-300ER - GE90</v>
       </c>
     </row>
     <row r="47">
@@ -15340,7 +15369,7 @@
         <v>G-YMMB</v>
       </c>
       <c r="C47" t="str">
-        <v>Boeing 777-200 - RR Trent 800</v>
+        <v>Boeing 777-200ER - RR Trent 800</v>
       </c>
     </row>
     <row r="48">
@@ -15351,7 +15380,7 @@
         <v>G-YMMF</v>
       </c>
       <c r="C48" t="str">
-        <v>Boeing 777-200 - RR Trent 800</v>
+        <v>Boeing 777-200ER - RR Trent 800</v>
       </c>
     </row>
     <row r="49">
@@ -15362,7 +15391,7 @@
         <v>G-YMMG</v>
       </c>
       <c r="C49" t="str">
-        <v>Boeing 777-200 - RR Trent 800</v>
+        <v>Boeing 777-200ER - RR Trent 800</v>
       </c>
     </row>
     <row r="50">
@@ -15373,7 +15402,7 @@
         <v>G-YMMI</v>
       </c>
       <c r="C50" t="str">
-        <v>Boeing 777-200 - RR Trent 800</v>
+        <v>Boeing 777-200ER - RR Trent 800</v>
       </c>
     </row>
     <row r="51">
@@ -15384,7 +15413,7 @@
         <v>G-YMMJ</v>
       </c>
       <c r="C51" t="str">
-        <v>Boeing 777-200 - RR Trent 800</v>
+        <v>Boeing 777-200ER - RR Trent 800</v>
       </c>
     </row>
     <row r="52">
@@ -15395,7 +15424,7 @@
         <v>G-YMMK</v>
       </c>
       <c r="C52" t="str">
-        <v>Boeing 777-200 - RR Trent 800</v>
+        <v>Boeing 777-200ER - RR Trent 800</v>
       </c>
     </row>
     <row r="53">
@@ -15406,7 +15435,7 @@
         <v>G-YMMP</v>
       </c>
       <c r="C53" t="str">
-        <v>Boeing 777-200 - RR Trent 800</v>
+        <v>Boeing 777-200ER - RR Trent 800</v>
       </c>
     </row>
     <row r="54">
@@ -15417,7 +15446,7 @@
         <v>G-YMMT</v>
       </c>
       <c r="C54" t="str">
-        <v>Boeing 777-200 - RR Trent 800</v>
+        <v>Boeing 777-200ER - RR Trent 800</v>
       </c>
     </row>
     <row r="55">
@@ -15428,7 +15457,7 @@
         <v>G-YMMU</v>
       </c>
       <c r="C55" t="str">
-        <v>Boeing 777-200 - RR Trent 800</v>
+        <v>Boeing 777-200ER - RR Trent 800</v>
       </c>
     </row>
     <row r="56">
@@ -15801,7 +15830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B73"/>
   <sheetData>
@@ -16396,7 +16425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F29"/>
   <sheetData>
@@ -16987,7 +17016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B4"/>
   <sheetData>

--- a/cap741-data.xlsx
+++ b/cap741-data.xlsx
@@ -1,34 +1,18 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>SheetJS</Application>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>Worksheets</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>5</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="5" baseType="lpstr">
-      <vt:lpstr>Logbook</vt:lpstr>
-      <vt:lpstr>Aircraft</vt:lpstr>
-      <vt:lpstr>Chapters</vt:lpstr>
-      <vt:lpstr>Supervisors</vt:lpstr>
-      <vt:lpstr>Info</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <sheets>
+    <sheet name="Logbook" sheetId="1" r:id="rId1"/>
+    <sheet name="Aircraft" sheetId="2" r:id="rId2"/>
+    <sheet name="Chapters" sheetId="3" r:id="rId3"/>
+    <sheet name="Supervisors" sheetId="4" r:id="rId4"/>
+    <sheet name="Info" sheetId="5" r:id="rId5"/>
+  </sheets>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance"/>
-</file>
-
-<file path=xl\metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
@@ -50,7 +34,7 @@
 </metadata>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
@@ -95,7 +79,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -415,22 +399,9 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
-  <sheets>
-    <sheet name="Logbook" sheetId="1" r:id="rId1"/>
-    <sheet name="Aircraft" sheetId="2" r:id="rId2"/>
-    <sheet name="Chapters" sheetId="3" r:id="rId3"/>
-    <sheet name="Supervisors" sheetId="4" r:id="rId4"/>
-    <sheet name="Info" sheetId="5" r:id="rId5"/>
-  </sheets>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L376"/>
+  <dimension ref="A1:M376"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -468,6 +439,9 @@
       </c>
       <c r="L1" t="str">
         <v>Aprroval Licence No.</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Signed</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
@@ -513,6 +487,9 @@
       <c r="L2" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
@@ -552,6 +529,9 @@
       </c>
       <c r="L3" t="str">
         <v>UK.66.429968K</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -613,6 +593,9 @@
       <c r="L4" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5" xml:space="preserve">
       <c r="A5" t="str">
@@ -662,6 +645,9 @@
       </c>
       <c r="L5" t="str">
         <v>UK.66.429968K</v>
+      </c>
+      <c r="M5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -718,6 +704,9 @@
       </c>
       <c r="L6" t="str">
         <v>UK.66.429968K</v>
+      </c>
+      <c r="M6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -821,6 +810,9 @@
       <c r="L7" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -859,6 +851,9 @@
       <c r="L8" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -897,6 +892,9 @@
       <c r="L9" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -935,6 +933,9 @@
       <c r="L10" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -973,6 +974,9 @@
       <c r="L11" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1011,6 +1015,9 @@
       <c r="L12" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1049,6 +1056,9 @@
       <c r="L13" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -1087,6 +1097,9 @@
       <c r="L14" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1125,6 +1138,9 @@
       <c r="L15" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1163,6 +1179,9 @@
       <c r="L16" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1201,6 +1220,9 @@
       <c r="L17" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1239,6 +1261,9 @@
       <c r="L18" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1277,6 +1302,9 @@
       <c r="L19" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1315,6 +1343,9 @@
       <c r="L20" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1353,6 +1384,9 @@
       <c r="L21" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1391,6 +1425,9 @@
       <c r="L22" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1429,6 +1466,9 @@
       <c r="L23" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1467,6 +1507,9 @@
       <c r="L24" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1505,6 +1548,9 @@
       <c r="L25" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1543,6 +1589,9 @@
       <c r="L26" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1581,6 +1630,9 @@
       <c r="L27" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1619,6 +1671,9 @@
       <c r="L28" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1657,6 +1712,9 @@
       <c r="L29" t="str">
         <v>UK.66.499953C</v>
       </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1695,6 +1753,9 @@
       <c r="L30" t="str">
         <v>UK.66.499953C</v>
       </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1733,6 +1794,9 @@
       <c r="L31" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1771,6 +1835,9 @@
       <c r="L32" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1809,6 +1876,9 @@
       <c r="L33" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1847,6 +1917,9 @@
       <c r="L34" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -1885,6 +1958,9 @@
       <c r="L35" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1923,6 +1999,9 @@
       <c r="L36" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1961,6 +2040,9 @@
       <c r="L37" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1999,6 +2081,9 @@
       <c r="L38" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -2037,6 +2122,9 @@
       <c r="L39" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -2075,6 +2163,9 @@
       <c r="L40" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -2113,6 +2204,9 @@
       <c r="L41" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M41" t="str">
+        <v>true</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -2151,6 +2245,9 @@
       <c r="L42" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2189,6 +2286,9 @@
       <c r="L43" t="str">
         <v>UK.66.499953C</v>
       </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2227,6 +2327,9 @@
       <c r="L44" t="str">
         <v>UK.66.499953C</v>
       </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2265,6 +2368,9 @@
       <c r="L45" t="str">
         <v>UK.66.499953C</v>
       </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2303,6 +2409,9 @@
       <c r="L46" t="str">
         <v>UK.66.499953C</v>
       </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2341,6 +2450,9 @@
       <c r="L47" t="str">
         <v>UK.66.499953C</v>
       </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2379,6 +2491,9 @@
       <c r="L48" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2417,6 +2532,9 @@
       <c r="L49" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2455,6 +2573,9 @@
       <c r="L50" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2493,6 +2614,9 @@
       <c r="L51" t="str">
         <v>UK.66.511681C</v>
       </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2531,6 +2655,9 @@
       <c r="L52" t="str">
         <v>UK.66.511681C</v>
       </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -2569,6 +2696,9 @@
       <c r="L53" t="str">
         <v>UK.66.511681C</v>
       </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -2607,6 +2737,9 @@
       <c r="L54" t="str">
         <v>UK.66.515457K</v>
       </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -2645,6 +2778,9 @@
       <c r="L55" t="str">
         <v>UK.66.515457K</v>
       </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -2683,6 +2819,9 @@
       <c r="L56" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -2721,6 +2860,9 @@
       <c r="L57" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -2759,6 +2901,9 @@
       <c r="L58" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -2797,6 +2942,9 @@
       <c r="L59" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -2835,6 +2983,9 @@
       <c r="L60" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -2873,6 +3024,9 @@
       <c r="L61" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -2911,6 +3065,9 @@
       <c r="L62" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -2949,6 +3106,9 @@
       <c r="L63" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -2987,6 +3147,9 @@
       <c r="L64" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -3025,6 +3188,9 @@
       <c r="L65" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -3063,6 +3229,9 @@
       <c r="L66" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -3101,6 +3270,9 @@
       <c r="L67" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -3139,6 +3311,9 @@
       <c r="L68" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -3177,6 +3352,9 @@
       <c r="L69" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -3215,6 +3393,9 @@
       <c r="L70" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -3253,6 +3434,9 @@
       <c r="L71" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -3291,6 +3475,9 @@
       <c r="L72" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -3329,6 +3516,9 @@
       <c r="L73" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -3367,6 +3557,9 @@
       <c r="L74" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -3405,6 +3598,9 @@
       <c r="L75" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -3443,6 +3639,9 @@
       <c r="L76" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -3481,6 +3680,9 @@
       <c r="L77" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -3519,6 +3721,9 @@
       <c r="L78" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -3557,6 +3762,9 @@
       <c r="L79" t="str">
         <v>Uk.145.00021</v>
       </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -3595,6 +3803,9 @@
       <c r="L80" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -3633,6 +3844,9 @@
       <c r="L81" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -3671,6 +3885,9 @@
       <c r="L82" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -3709,6 +3926,9 @@
       <c r="L83" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -3747,6 +3967,9 @@
       <c r="L84" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -3785,6 +4008,9 @@
       <c r="L85" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -3823,6 +4049,9 @@
       <c r="L86" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -3861,6 +4090,9 @@
       <c r="L87" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -3899,6 +4131,9 @@
       <c r="L88" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -3937,6 +4172,9 @@
       <c r="L89" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -3975,6 +4213,9 @@
       <c r="L90" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -4013,6 +4254,9 @@
       <c r="L91" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -4051,6 +4295,9 @@
       <c r="L92" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -4089,6 +4336,9 @@
       <c r="L93" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -4127,6 +4377,9 @@
       <c r="L94" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -4165,6 +4418,9 @@
       <c r="L95" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -4203,6 +4459,9 @@
       <c r="L96" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -4241,6 +4500,9 @@
       <c r="L97" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -4279,6 +4541,9 @@
       <c r="L98" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -4317,6 +4582,9 @@
       <c r="L99" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -4355,6 +4623,9 @@
       <c r="L100" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -4393,6 +4664,9 @@
       <c r="L101" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -4431,6 +4705,9 @@
       <c r="L102" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -4469,6 +4746,9 @@
       <c r="L103" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -4507,6 +4787,9 @@
       <c r="L104" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -4545,6 +4828,9 @@
       <c r="L105" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -4583,6 +4869,9 @@
       <c r="L106" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -4621,6 +4910,9 @@
       <c r="L107" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -4659,6 +4951,9 @@
       <c r="L108" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -4697,6 +4992,9 @@
       <c r="L109" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -4735,6 +5033,9 @@
       <c r="L110" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -4773,6 +5074,9 @@
       <c r="L111" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -4811,6 +5115,9 @@
       <c r="L112" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -4849,6 +5156,9 @@
       <c r="L113" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -4887,6 +5197,9 @@
       <c r="L114" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -4925,6 +5238,9 @@
       <c r="L115" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -4963,6 +5279,9 @@
       <c r="L116" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -5001,6 +5320,9 @@
       <c r="L117" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -5039,6 +5361,9 @@
       <c r="L118" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -5077,6 +5402,9 @@
       <c r="L119" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -5115,6 +5443,9 @@
       <c r="L120" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -5153,6 +5484,9 @@
       <c r="L121" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -5191,6 +5525,9 @@
       <c r="L122" t="str">
         <v>UK.66.455016A</v>
       </c>
+      <c r="M122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -5229,6 +5566,9 @@
       <c r="L123" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -5267,6 +5607,9 @@
       <c r="L124" t="str">
         <v>UK.66.515457K</v>
       </c>
+      <c r="M124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -5305,6 +5648,9 @@
       <c r="L125" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -5343,6 +5689,9 @@
       <c r="L126" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -5381,6 +5730,9 @@
       <c r="L127" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -5419,6 +5771,9 @@
       <c r="L128" t="str">
         <v>UK.66.499953C</v>
       </c>
+      <c r="M128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -5457,6 +5812,9 @@
       <c r="L129" t="str">
         <v>UK.66.499953C</v>
       </c>
+      <c r="M129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -5495,6 +5853,9 @@
       <c r="L130" t="str">
         <v>UK.66.499953C</v>
       </c>
+      <c r="M130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -5533,6 +5894,9 @@
       <c r="L131" t="str">
         <v>UK.66.499953C</v>
       </c>
+      <c r="M131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -5571,6 +5935,9 @@
       <c r="L132" t="str">
         <v>UK.66.499953C</v>
       </c>
+      <c r="M132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -5609,6 +5976,9 @@
       <c r="L133" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -5647,6 +6017,9 @@
       <c r="L134" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -5685,6 +6058,9 @@
       <c r="L135" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -5723,6 +6099,9 @@
       <c r="L136" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -5761,6 +6140,9 @@
       <c r="L137" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -5799,6 +6181,9 @@
       <c r="L138" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -5837,6 +6222,9 @@
       <c r="L139" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -5875,6 +6263,9 @@
       <c r="L140" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -5913,6 +6304,9 @@
       <c r="L141" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -5951,6 +6345,9 @@
       <c r="L142" t="str">
         <v>UK.66.511681C</v>
       </c>
+      <c r="M142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -5989,6 +6386,9 @@
       <c r="L143" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -6027,6 +6427,9 @@
       <c r="L144" t="str">
         <v>UK.66.511681C</v>
       </c>
+      <c r="M144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -6065,6 +6468,9 @@
       <c r="L145" t="str">
         <v>UK.66.499953C</v>
       </c>
+      <c r="M145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -6103,6 +6509,9 @@
       <c r="L146" t="str">
         <v>UK.66.515457K</v>
       </c>
+      <c r="M146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -6141,6 +6550,9 @@
       <c r="L147" t="str">
         <v>UK66.439742H</v>
       </c>
+      <c r="M147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -6179,6 +6591,9 @@
       <c r="L148" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -6217,6 +6632,9 @@
       <c r="L149" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -6255,6 +6673,9 @@
       <c r="L150" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -6293,6 +6714,9 @@
       <c r="L151" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -6331,6 +6755,9 @@
       <c r="L152" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -6369,6 +6796,9 @@
       <c r="L153" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -6407,6 +6837,9 @@
       <c r="L154" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -6445,6 +6878,9 @@
       <c r="L155" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -6483,6 +6919,9 @@
       <c r="L156" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -6521,6 +6960,9 @@
       <c r="L157" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -6559,6 +7001,9 @@
       <c r="L158" t="str">
         <v>UK.66.576876E</v>
       </c>
+      <c r="M158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -6597,6 +7042,9 @@
       <c r="L159" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -6635,6 +7083,9 @@
       <c r="L160" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -6673,6 +7124,9 @@
       <c r="L161" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -6711,6 +7165,9 @@
       <c r="L162" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -6749,6 +7206,9 @@
       <c r="L163" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -6787,6 +7247,9 @@
       <c r="L164" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M164" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -6825,6 +7288,9 @@
       <c r="L165" t="str">
         <v>UK.66.511681C</v>
       </c>
+      <c r="M165" t="str">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -6863,6 +7329,9 @@
       <c r="L166" t="str">
         <v/>
       </c>
+      <c r="M166" t="str">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -6901,6 +7370,9 @@
       <c r="L167" t="str">
         <v>UK.66.335215C</v>
       </c>
+      <c r="M167" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -6939,6 +7411,9 @@
       <c r="L168" t="str">
         <v>UK.66.511681C</v>
       </c>
+      <c r="M168" t="str">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -6977,6 +7452,9 @@
       <c r="L169" t="str">
         <v>UK.66.511681C</v>
       </c>
+      <c r="M169" t="str">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -7015,6 +7493,9 @@
       <c r="L170" t="str">
         <v>UK.66.511681C</v>
       </c>
+      <c r="M170" t="str">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -7053,6 +7534,9 @@
       <c r="L171" t="str">
         <v>UK.66.576876E</v>
       </c>
+      <c r="M171" t="str">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -7091,6 +7575,9 @@
       <c r="L172" t="str">
         <v>UK.66.576876E</v>
       </c>
+      <c r="M172" t="str">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -7129,6 +7616,9 @@
       <c r="L173" t="str">
         <v>UK.66.576876E</v>
       </c>
+      <c r="M173" t="str">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -7167,6 +7657,9 @@
       <c r="L174" t="str">
         <v>UK.66.576876E</v>
       </c>
+      <c r="M174" t="str">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -7205,6 +7698,9 @@
       <c r="L175" t="str">
         <v>UK.66.576876E</v>
       </c>
+      <c r="M175" t="str">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -7243,6 +7739,9 @@
       <c r="L176" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M176" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -7281,6 +7780,9 @@
       <c r="L177" t="str">
         <v>UK.66.576876E</v>
       </c>
+      <c r="M177" t="str">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -7319,6 +7821,9 @@
       <c r="L178" t="str">
         <v>UK.66.576876E</v>
       </c>
+      <c r="M178" t="str">
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -7357,6 +7862,9 @@
       <c r="L179" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M179" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -7395,6 +7903,9 @@
       <c r="L180" t="str">
         <v>UK.66.515457K</v>
       </c>
+      <c r="M180" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -7433,6 +7944,9 @@
       <c r="L181" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -7471,6 +7985,9 @@
       <c r="L182" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -7509,6 +8026,9 @@
       <c r="L183" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -7547,6 +8067,9 @@
       <c r="L184" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -7585,6 +8108,9 @@
       <c r="L185" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M185" t="str">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -7623,6 +8149,9 @@
       <c r="L186" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -7661,6 +8190,9 @@
       <c r="L187" t="str">
         <v>UK.66.515457K</v>
       </c>
+      <c r="M187" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -7699,6 +8231,9 @@
       <c r="L188" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M188" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -7737,6 +8272,9 @@
       <c r="L189" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M189" t="str">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -7775,6 +8313,9 @@
       <c r="L190" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M190" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -7813,6 +8354,9 @@
       <c r="L191" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M191" t="str">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -7851,6 +8395,9 @@
       <c r="L192" t="str">
         <v>UK.66.335215C</v>
       </c>
+      <c r="M192" t="str">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -7889,6 +8436,9 @@
       <c r="L193" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M193" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -7927,6 +8477,9 @@
       <c r="L194" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M194" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -7965,6 +8518,9 @@
       <c r="L195" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M195" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -8003,6 +8559,9 @@
       <c r="L196" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M196" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -8041,6 +8600,9 @@
       <c r="L197" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M197" t="str">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -8079,6 +8641,9 @@
       <c r="L198" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M198" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -8117,6 +8682,9 @@
       <c r="L199" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M199" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -8155,6 +8723,9 @@
       <c r="L200" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M200" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -8193,6 +8764,9 @@
       <c r="L201" t="str">
         <v>UK66 413528H</v>
       </c>
+      <c r="M201" t="str">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -8231,6 +8805,9 @@
       <c r="L202" t="str">
         <v>UK66.439742H</v>
       </c>
+      <c r="M202" t="str">
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -8269,6 +8846,9 @@
       <c r="L203" t="str">
         <v>UK66.439742H</v>
       </c>
+      <c r="M203" t="str">
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -8307,6 +8887,9 @@
       <c r="L204" t="str">
         <v>UK66.439742H</v>
       </c>
+      <c r="M204" t="str">
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -8345,6 +8928,9 @@
       <c r="L205" t="str">
         <v>UK66.439742H</v>
       </c>
+      <c r="M205" t="str">
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -8383,6 +8969,9 @@
       <c r="L206" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M206" t="str">
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -8421,6 +9010,9 @@
       <c r="L207" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M207" t="str">
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -8459,6 +9051,9 @@
       <c r="L208" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M208" t="str">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -8497,6 +9092,9 @@
       <c r="L209" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M209" t="str">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -8535,6 +9133,9 @@
       <c r="L210" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M210" t="str">
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -8573,6 +9174,9 @@
       <c r="L211" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M211" t="str">
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -8611,6 +9215,9 @@
       <c r="L212" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M212" t="str">
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -8649,6 +9256,9 @@
       <c r="L213" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M213" t="str">
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -8687,6 +9297,9 @@
       <c r="L214" t="str">
         <v>UK.66.576876E</v>
       </c>
+      <c r="M214" t="str">
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -8725,6 +9338,9 @@
       <c r="L215" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M215" t="str">
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -8763,6 +9379,9 @@
       <c r="L216" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M216" t="str">
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -8801,6 +9420,9 @@
       <c r="L217" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M217" t="str">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -8839,6 +9461,9 @@
       <c r="L218" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M218" t="str">
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -8877,6 +9502,9 @@
       <c r="L219" t="str">
         <v>UK.66.455016A</v>
       </c>
+      <c r="M219" t="str">
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -8915,6 +9543,9 @@
       <c r="L220" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M220" t="str">
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -8953,6 +9584,9 @@
       <c r="L221" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M221" t="str">
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -8991,6 +9625,9 @@
       <c r="L222" t="str">
         <v/>
       </c>
+      <c r="M222" t="str">
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -9029,6 +9666,9 @@
       <c r="L223" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M223" t="str">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -9067,6 +9707,9 @@
       <c r="L224" t="str">
         <v/>
       </c>
+      <c r="M224" t="str">
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -9105,6 +9748,9 @@
       <c r="L225" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M225" t="str">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -9143,6 +9789,9 @@
       <c r="L226" t="str">
         <v>UK.66.335215C</v>
       </c>
+      <c r="M226" t="str">
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -9181,6 +9830,9 @@
       <c r="L227" t="str">
         <v/>
       </c>
+      <c r="M227" t="str">
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -9219,6 +9871,9 @@
       <c r="L228" t="str">
         <v/>
       </c>
+      <c r="M228" t="str">
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -9257,6 +9912,9 @@
       <c r="L229" t="str">
         <v/>
       </c>
+      <c r="M229" t="str">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -9295,6 +9953,9 @@
       <c r="L230" t="str">
         <v/>
       </c>
+      <c r="M230" t="str">
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -9333,6 +9994,9 @@
       <c r="L231" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M231" t="str">
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -9371,6 +10035,9 @@
       <c r="L232" t="str">
         <v/>
       </c>
+      <c r="M232" t="str">
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -9409,6 +10076,9 @@
       <c r="L233" t="str">
         <v>UK.66.455016A</v>
       </c>
+      <c r="M233" t="str">
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -9447,6 +10117,9 @@
       <c r="L234" t="str">
         <v/>
       </c>
+      <c r="M234" t="str">
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -9485,6 +10158,9 @@
       <c r="L235" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M235" t="str">
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -9523,6 +10199,9 @@
       <c r="L236" t="str">
         <v/>
       </c>
+      <c r="M236" t="str">
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -9561,6 +10240,9 @@
       <c r="L237" t="str">
         <v>UK66 413528H</v>
       </c>
+      <c r="M237" t="str">
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -9599,6 +10281,9 @@
       <c r="L238" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M238" t="str">
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -9637,6 +10322,9 @@
       <c r="L239" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M239" t="str">
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -9675,6 +10363,9 @@
       <c r="L240" t="str">
         <v>UK.66.576876E</v>
       </c>
+      <c r="M240" t="str">
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -9713,6 +10404,9 @@
       <c r="L241" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M241" t="str">
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -9751,6 +10445,9 @@
       <c r="L242" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M242" t="str">
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -9789,6 +10486,9 @@
       <c r="L243" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M243" t="str">
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -9827,6 +10527,9 @@
       <c r="L244" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M244" t="str">
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -9865,6 +10568,9 @@
       <c r="L245" t="str">
         <v/>
       </c>
+      <c r="M245" t="str">
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -9903,6 +10609,9 @@
       <c r="L246" t="str">
         <v>UK66.439742H</v>
       </c>
+      <c r="M246" t="str">
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -9941,6 +10650,9 @@
       <c r="L247" t="str">
         <v/>
       </c>
+      <c r="M247" t="str">
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -9979,6 +10691,9 @@
       <c r="L248" t="str">
         <v/>
       </c>
+      <c r="M248" t="str">
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -10017,6 +10732,9 @@
       <c r="L249" t="str">
         <v>UK.66.576876E</v>
       </c>
+      <c r="M249" t="str">
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -10055,6 +10773,9 @@
       <c r="L250" t="str">
         <v/>
       </c>
+      <c r="M250" t="str">
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -10093,6 +10814,9 @@
       <c r="L251" t="str">
         <v>UK.66.455016A</v>
       </c>
+      <c r="M251" t="str">
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -10131,6 +10855,9 @@
       <c r="L252" t="str">
         <v/>
       </c>
+      <c r="M252" t="str">
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -10169,6 +10896,9 @@
       <c r="L253" t="str">
         <v>UK.66.461676F</v>
       </c>
+      <c r="M253" t="str">
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -10207,6 +10937,9 @@
       <c r="L254" t="str">
         <v/>
       </c>
+      <c r="M254" t="str">
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -10245,6 +10978,9 @@
       <c r="L255" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M255" t="str">
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -10283,6 +11019,9 @@
       <c r="L256" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M256" t="str">
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -10321,6 +11060,9 @@
       <c r="L257" t="str">
         <v/>
       </c>
+      <c r="M257" t="str">
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -10359,6 +11101,9 @@
       <c r="L258" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M258" t="str">
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -10397,6 +11142,9 @@
       <c r="L259" t="str">
         <v>UK.66.515457K</v>
       </c>
+      <c r="M259" t="str">
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -10435,6 +11183,9 @@
       <c r="L260" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M260" t="str">
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
@@ -10473,6 +11224,9 @@
       <c r="L261" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M261" t="str">
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -10511,6 +11265,9 @@
       <c r="L262" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M262" t="str">
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -10549,6 +11306,9 @@
       <c r="L263" t="str">
         <v>UK.66.429968K</v>
       </c>
+      <c r="M263" t="str">
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
@@ -10587,6 +11347,9 @@
       <c r="L264" t="str">
         <v>UK.66.455016A</v>
       </c>
+      <c r="M264" t="str">
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
@@ -10625,6 +11388,9 @@
       <c r="L265" t="str">
         <v/>
       </c>
+      <c r="M265" t="str">
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
@@ -10663,6 +11429,9 @@
       <c r="L266" t="str">
         <v/>
       </c>
+      <c r="M266" t="str">
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -10701,6 +11470,9 @@
       <c r="L267" t="str">
         <v>UK.66.335215C</v>
       </c>
+      <c r="M267" t="str">
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -10739,6 +11511,9 @@
       <c r="L268" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M268" t="str">
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -10777,6 +11552,9 @@
       <c r="L269" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M269" t="str">
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
@@ -10815,6 +11593,9 @@
       <c r="L270" t="str">
         <v/>
       </c>
+      <c r="M270" t="str">
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -10853,6 +11634,9 @@
       <c r="L271" t="str">
         <v>UK.66.515457K</v>
       </c>
+      <c r="M271" t="str">
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
@@ -10891,6 +11675,9 @@
       <c r="L272" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M272" t="str">
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
@@ -10929,6 +11716,9 @@
       <c r="L273" t="str">
         <v>UK.66.487984E</v>
       </c>
+      <c r="M273" t="str">
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
@@ -10967,6 +11757,9 @@
       <c r="L274" t="str">
         <v/>
       </c>
+      <c r="M274" t="str">
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -11005,6 +11798,9 @@
       <c r="L275" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M275" t="str">
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -11043,6 +11839,9 @@
       <c r="L276" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M276" t="str">
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -11081,6 +11880,9 @@
       <c r="L277" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M277" t="str">
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -11119,6 +11921,9 @@
       <c r="L278" t="str">
         <v/>
       </c>
+      <c r="M278" t="str">
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -11157,6 +11962,9 @@
       <c r="L279" t="str">
         <v>UK.66.515457K</v>
       </c>
+      <c r="M279" t="str">
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -11195,6 +12003,9 @@
       <c r="L280" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M280" t="str">
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
@@ -11233,6 +12044,9 @@
       <c r="L281" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M281" t="str">
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
@@ -11271,6 +12085,9 @@
       <c r="L282" t="str">
         <v>UK.66.511681C</v>
       </c>
+      <c r="M282" t="str">
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
@@ -11309,6 +12126,9 @@
       <c r="L283" t="str">
         <v>UK.66.511681C</v>
       </c>
+      <c r="M283" t="str">
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
@@ -11347,6 +12167,9 @@
       <c r="L284" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M284" t="str">
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
@@ -11385,6 +12208,9 @@
       <c r="L285" t="str">
         <v>UK.66.511681C</v>
       </c>
+      <c r="M285" t="str">
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -11423,6 +12249,9 @@
       <c r="L286" t="str">
         <v>UK.66.511681C</v>
       </c>
+      <c r="M286" t="str">
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
@@ -11461,6 +12290,9 @@
       <c r="L287" t="str">
         <v>UK.66.511681C</v>
       </c>
+      <c r="M287" t="str">
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
@@ -11499,6 +12331,9 @@
       <c r="L288" t="str">
         <v/>
       </c>
+      <c r="M288" t="str">
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
@@ -11537,6 +12372,9 @@
       <c r="L289" t="str">
         <v>UK66 413528H</v>
       </c>
+      <c r="M289" t="str">
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
@@ -11575,6 +12413,9 @@
       <c r="L290" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M290" t="str">
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
@@ -11613,6 +12454,9 @@
       <c r="L291" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M291" t="str">
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
@@ -11651,6 +12495,9 @@
       <c r="L292" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M292" t="str">
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
@@ -11689,6 +12536,9 @@
       <c r="L293" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M293" t="str">
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
@@ -11727,6 +12577,9 @@
       <c r="L294" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M294" t="str">
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
@@ -11765,6 +12618,9 @@
       <c r="L295" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M295" t="str">
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
@@ -11803,6 +12659,9 @@
       <c r="L296" t="str">
         <v>UK.66.455016A</v>
       </c>
+      <c r="M296" t="str">
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
@@ -11841,6 +12700,9 @@
       <c r="L297" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M297" t="str">
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
@@ -11879,6 +12741,9 @@
       <c r="L298" t="str">
         <v>UK.66.455016A</v>
       </c>
+      <c r="M298" t="str">
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
@@ -11917,6 +12782,9 @@
       <c r="L299" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M299" t="str">
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
@@ -11955,6 +12823,9 @@
       <c r="L300" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M300" t="str">
+        <v/>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -11993,6 +12864,9 @@
       <c r="L301" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M301" t="str">
+        <v/>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
@@ -12031,6 +12905,9 @@
       <c r="L302" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M302" t="str">
+        <v/>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -12069,6 +12946,9 @@
       <c r="L303" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M303" t="str">
+        <v/>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -12107,6 +12987,9 @@
       <c r="L304" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M304" t="str">
+        <v/>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -12145,6 +13028,9 @@
       <c r="L305" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M305" t="str">
+        <v/>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
@@ -12183,6 +13069,9 @@
       <c r="L306" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M306" t="str">
+        <v/>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -12221,6 +13110,9 @@
       <c r="L307" t="str">
         <v>UK.66.515457K</v>
       </c>
+      <c r="M307" t="str">
+        <v/>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
@@ -12259,6 +13151,9 @@
       <c r="L308" t="str">
         <v>UK.66.515457K</v>
       </c>
+      <c r="M308" t="str">
+        <v/>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
@@ -12297,6 +13192,9 @@
       <c r="L309" t="str">
         <v>UK.66.515457K</v>
       </c>
+      <c r="M309" t="str">
+        <v/>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
@@ -12335,6 +13233,9 @@
       <c r="L310" t="str">
         <v>UK.66.515457K</v>
       </c>
+      <c r="M310" t="str">
+        <v/>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
@@ -12373,6 +13274,9 @@
       <c r="L311" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M311" t="str">
+        <v/>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
@@ -12411,6 +13315,9 @@
       <c r="L312" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M312" t="str">
+        <v/>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
@@ -12449,6 +13356,9 @@
       <c r="L313" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M313" t="str">
+        <v/>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -12487,6 +13397,9 @@
       <c r="L314" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M314" t="str">
+        <v/>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -12525,6 +13438,9 @@
       <c r="L315" t="str">
         <v/>
       </c>
+      <c r="M315" t="str">
+        <v/>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
@@ -12563,6 +13479,9 @@
       <c r="L316" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M316" t="str">
+        <v/>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
@@ -12601,6 +13520,9 @@
       <c r="L317" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M317" t="str">
+        <v/>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
@@ -12639,6 +13561,9 @@
       <c r="L318" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M318" t="str">
+        <v/>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
@@ -12677,6 +13602,9 @@
       <c r="L319" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M319" t="str">
+        <v/>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
@@ -12715,6 +13643,9 @@
       <c r="L320" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M320" t="str">
+        <v/>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
@@ -12753,6 +13684,9 @@
       <c r="L321" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M321" t="str">
+        <v/>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
@@ -12791,6 +13725,9 @@
       <c r="L322" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M322" t="str">
+        <v/>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
@@ -12829,6 +13766,9 @@
       <c r="L323" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M323" t="str">
+        <v/>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
@@ -12867,6 +13807,9 @@
       <c r="L324" t="str">
         <v/>
       </c>
+      <c r="M324" t="str">
+        <v/>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
@@ -12905,6 +13848,9 @@
       <c r="L325" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M325" t="str">
+        <v/>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
@@ -12943,6 +13889,9 @@
       <c r="L326" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M326" t="str">
+        <v/>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
@@ -12981,6 +13930,9 @@
       <c r="L327" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M327" t="str">
+        <v/>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
@@ -13019,6 +13971,9 @@
       <c r="L328" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M328" t="str">
+        <v/>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
@@ -13057,6 +14012,9 @@
       <c r="L329" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M329" t="str">
+        <v/>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
@@ -13095,6 +14053,9 @@
       <c r="L330" t="str">
         <v>UK.66.455016A</v>
       </c>
+      <c r="M330" t="str">
+        <v/>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
@@ -13133,6 +14094,9 @@
       <c r="L331" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M331" t="str">
+        <v/>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
@@ -13171,6 +14135,9 @@
       <c r="L332" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M332" t="str">
+        <v/>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
@@ -13209,6 +14176,9 @@
       <c r="L333" t="str">
         <v>UK66 413528H</v>
       </c>
+      <c r="M333" t="str">
+        <v/>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
@@ -13247,6 +14217,9 @@
       <c r="L334" t="str">
         <v>UK66 413528H</v>
       </c>
+      <c r="M334" t="str">
+        <v/>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
@@ -13285,6 +14258,9 @@
       <c r="L335" t="str">
         <v>UK.66.445183K</v>
       </c>
+      <c r="M335" t="str">
+        <v/>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
@@ -13323,6 +14299,9 @@
       <c r="L336" t="str">
         <v>UK66 413528H</v>
       </c>
+      <c r="M336" t="str">
+        <v/>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
@@ -13361,6 +14340,9 @@
       <c r="L337" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M337" t="str">
+        <v/>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
@@ -13399,6 +14381,9 @@
       <c r="L338" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M338" t="str">
+        <v/>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
@@ -13437,6 +14422,9 @@
       <c r="L339" t="str">
         <v>UK.66.455631C</v>
       </c>
+      <c r="M339" t="str">
+        <v/>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
@@ -13475,6 +14463,9 @@
       <c r="L340" t="str">
         <v>UK.66.455016A</v>
       </c>
+      <c r="M340" t="str">
+        <v/>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
@@ -13513,6 +14504,9 @@
       <c r="L341" t="str">
         <v>UK.66.473350J</v>
       </c>
+      <c r="M341" t="str">
+        <v/>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
@@ -13551,6 +14545,9 @@
       <c r="L342" t="str">
         <v>UK66 413528H</v>
       </c>
+      <c r="M342" t="str">
+        <v/>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
@@ -13589,6 +14586,9 @@
       <c r="L343" t="str">
         <v>UK66 413528H</v>
       </c>
+      <c r="M343" t="str">
+        <v/>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
@@ -13627,6 +14627,9 @@
       <c r="L344" t="str">
         <v>UK66 413528H</v>
       </c>
+      <c r="M344" t="str">
+        <v/>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
@@ -13665,6 +14668,9 @@
       <c r="L345" t="str">
         <v>UK66 413528H</v>
       </c>
+      <c r="M345" t="str">
+        <v/>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
@@ -13703,6 +14709,9 @@
       <c r="L346" t="str">
         <v>UK.66.473350J</v>
       </c>
+      <c r="M346" t="str">
+        <v/>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
@@ -13741,6 +14750,9 @@
       <c r="L347" t="str">
         <v>UK.66.473350J</v>
       </c>
+      <c r="M347" t="str">
+        <v/>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
@@ -13779,6 +14791,9 @@
       <c r="L348" t="str">
         <v>UK.66.473350J</v>
       </c>
+      <c r="M348" t="str">
+        <v/>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
@@ -13817,6 +14832,9 @@
       <c r="L349" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M349" t="str">
+        <v/>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
@@ -13855,6 +14873,9 @@
       <c r="L350" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M350" t="str">
+        <v/>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
@@ -13893,6 +14914,9 @@
       <c r="L351" t="str">
         <v>UK.66.431179E</v>
       </c>
+      <c r="M351" t="str">
+        <v/>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
@@ -13931,6 +14955,9 @@
       <c r="L352" t="str">
         <v>UK.66.473350J</v>
       </c>
+      <c r="M352" t="str">
+        <v/>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
@@ -13969,6 +14996,9 @@
       <c r="L353" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M353" t="str">
+        <v/>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
@@ -14007,6 +15037,9 @@
       <c r="L354" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M354" t="str">
+        <v/>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
@@ -14045,6 +15078,9 @@
       <c r="L355" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M355" t="str">
+        <v/>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
@@ -14083,6 +15119,9 @@
       <c r="L356" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M356" t="str">
+        <v/>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
@@ -14121,6 +15160,9 @@
       <c r="L357" t="str">
         <v>UK.145.00021</v>
       </c>
+      <c r="M357" t="str">
+        <v/>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
@@ -14159,6 +15201,9 @@
       <c r="L358" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M358" t="str">
+        <v/>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
@@ -14197,6 +15242,9 @@
       <c r="L359" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M359" t="str">
+        <v/>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
@@ -14235,6 +15283,9 @@
       <c r="L360" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M360" t="str">
+        <v/>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
@@ -14273,6 +15324,9 @@
       <c r="L361" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M361" t="str">
+        <v/>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
@@ -14311,6 +15365,9 @@
       <c r="L362" t="str">
         <v>UK.66.455016A</v>
       </c>
+      <c r="M362" t="str">
+        <v/>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
@@ -14349,6 +15406,9 @@
       <c r="L363" t="str">
         <v>UK.66.473350J</v>
       </c>
+      <c r="M363" t="str">
+        <v/>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
@@ -14387,6 +15447,9 @@
       <c r="L364" t="str">
         <v>UK.66.473350J</v>
       </c>
+      <c r="M364" t="str">
+        <v/>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
@@ -14425,6 +15488,9 @@
       <c r="L365" t="str">
         <v>UK.66.473350J</v>
       </c>
+      <c r="M365" t="str">
+        <v/>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
@@ -14463,6 +15529,9 @@
       <c r="L366" t="str">
         <v>UK.66.473350J</v>
       </c>
+      <c r="M366" t="str">
+        <v/>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
@@ -14501,6 +15570,9 @@
       <c r="L367" t="str">
         <v>UK.66.473350J</v>
       </c>
+      <c r="M367" t="str">
+        <v/>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
@@ -14539,6 +15611,9 @@
       <c r="L368" t="str">
         <v>UK.66.473350J</v>
       </c>
+      <c r="M368" t="str">
+        <v/>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
@@ -14577,6 +15652,9 @@
       <c r="L369" t="str">
         <v>UK.66.473350J</v>
       </c>
+      <c r="M369" t="str">
+        <v/>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
@@ -14615,6 +15693,9 @@
       <c r="L370" t="str">
         <v>UK.66.473350J</v>
       </c>
+      <c r="M370" t="str">
+        <v/>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
@@ -14653,6 +15734,9 @@
       <c r="L371" t="str">
         <v>UK.66.473350J</v>
       </c>
+      <c r="M371" t="str">
+        <v/>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
@@ -14691,6 +15775,9 @@
       <c r="L372" t="str">
         <v>UK.66.335215C</v>
       </c>
+      <c r="M372" t="str">
+        <v/>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
@@ -14729,6 +15816,9 @@
       <c r="L373" t="str">
         <v>UK.66.412845A</v>
       </c>
+      <c r="M373" t="str">
+        <v/>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
@@ -14767,6 +15857,9 @@
       <c r="L374" t="str">
         <v>UK.66.419934L</v>
       </c>
+      <c r="M374" t="str">
+        <v/>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
@@ -14805,6 +15898,9 @@
       <c r="L375" t="str">
         <v>UK.66.415204B</v>
       </c>
+      <c r="M375" t="str">
+        <v/>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
@@ -14843,15 +15939,18 @@
       <c r="L376" t="str">
         <v/>
       </c>
+      <c r="M376" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L376"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M376"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C88"/>
   <sheetData>
@@ -15830,7 +16929,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B73"/>
   <sheetData>
@@ -16425,7 +17524,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F29"/>
   <sheetData>
@@ -17016,7 +18115,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B4"/>
   <sheetData>

--- a/cap741-data.xlsx
+++ b/cap741-data.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M376"/>
+  <dimension ref="A1:M377"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10487,7 +10487,7 @@
         <v>UK.66.412845A</v>
       </c>
       <c r="M243" t="str">
-        <v/>
+        <v>true</v>
       </c>
     </row>
     <row r="244">
@@ -15943,9 +15943,50 @@
         <v/>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>Airbus A350-1000 - RR Trent XWB-97</v>
+      </c>
+      <c r="B377" t="str">
+        <v>G-XWBD</v>
+      </c>
+      <c r="C377" t="str">
+        <v>5</v>
+      </c>
+      <c r="D377" t="str">
+        <v>Time Limits/Maintenance Checks</v>
+      </c>
+      <c r="E377" t="str">
+        <v>01/Apr/2026</v>
+      </c>
+      <c r="F377" t="str">
+        <v/>
+      </c>
+      <c r="G377" t="str">
+        <v/>
+      </c>
+      <c r="H377" t="str">
+        <v/>
+      </c>
+      <c r="I377" t="str">
+        <v>hello</v>
+      </c>
+      <c r="J377" t="str">
+        <v>David Needham</v>
+      </c>
+      <c r="K377" t="str">
+        <v>BX.1429</v>
+      </c>
+      <c r="L377" t="str">
+        <v>UK66 413528H</v>
+      </c>
+      <c r="M377" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M376"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M377"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/cap741-data.xlsx
+++ b/cap741-data.xlsx
@@ -10449,7 +10449,7 @@
         <v/>
       </c>
     </row>
-    <row r="243">
+    <row r="243" xml:space="preserve">
       <c r="A243" t="str">
         <v>Airbus A350-1000 - RR Trent XWB-97</v>
       </c>
@@ -10474,8 +10474,9 @@
       <c r="H243" t="str">
         <v>PERIODIC GROUND CHECK AT 7-DAY INTERVALS CARRIED OUT IAW DIR 10317077 PT 000 VERS 01. SEE SAP REVISION 01315524 DCN 001, 002 AND 003 FOR DETAILS</v>
       </c>
-      <c r="I243" t="str">
-        <v>Assisted with PERIODIC GROUND CHECK AT 7-DAY INTERVALS CARRIED OUT IAW DIR 10317077 PT 000 VERS 01. SEE SAP REVISION 01315524 DCN 001, 002 AND 003 FOR DETAILS for Action Maintenance Notification 40152456 - D7 NOTIFICATION, WBC STORAGE 7 DAY PE- D7 NOTIFICATION, W...c</v>
+      <c r="I243" t="str" xml:space="preserve">
+        <v xml:space="preserve">Assisted with PERIODIC GROUND CHECK AT 7-DAY INTERVALS CARRIED OUT IAW DIR 10317077 PT 000 VERS 01. SEE SAP REVISION 01315524 DCN 001, 002 AND 003 FOR DETAILS for Action Maintenance Notification 40152456 - D7 NOTIFICATION, WBC STORAGE 7 DAY PE- D7 NOTIFICATION, W...c
+Assisted with PERIODIC GROUND CHECK AT 7-DAY INTERVALS CARRIED OUT IAW DIR 10317077 PT 000 VERS 01. SEE SAP REVISION 01315524 DCN 001, 002 AND 003 FOR DETAILS for Action Maintenance Notification 40152456 - D7 NOTIFICATION, WBC STORAGE 7 DAY PE- D7 NOTIFICATION, W...c</v>
       </c>
       <c r="J243" t="str">
         <v>Kevin Cosgrave</v>
@@ -10487,7 +10488,7 @@
         <v>UK.66.412845A</v>
       </c>
       <c r="M243" t="str">
-        <v>true</v>
+        <v/>
       </c>
     </row>
     <row r="244">
@@ -15969,7 +15970,7 @@
         <v/>
       </c>
       <c r="I377" t="str">
-        <v>hello</v>
+        <v>hellovvv   tewrw</v>
       </c>
       <c r="J377" t="str">
         <v>David Needham</v>

--- a/cap741-data.xlsx
+++ b/cap741-data.xlsx
@@ -10449,7 +10449,7 @@
         <v/>
       </c>
     </row>
-    <row r="243" xml:space="preserve">
+    <row r="243">
       <c r="A243" t="str">
         <v>Airbus A350-1000 - RR Trent XWB-97</v>
       </c>
@@ -10474,9 +10474,8 @@
       <c r="H243" t="str">
         <v>PERIODIC GROUND CHECK AT 7-DAY INTERVALS CARRIED OUT IAW DIR 10317077 PT 000 VERS 01. SEE SAP REVISION 01315524 DCN 001, 002 AND 003 FOR DETAILS</v>
       </c>
-      <c r="I243" t="str" xml:space="preserve">
-        <v xml:space="preserve">Assisted with PERIODIC GROUND CHECK AT 7-DAY INTERVALS CARRIED OUT IAW DIR 10317077 PT 000 VERS 01. SEE SAP REVISION 01315524 DCN 001, 002 AND 003 FOR DETAILS for Action Maintenance Notification 40152456 - D7 NOTIFICATION, WBC STORAGE 7 DAY PE- D7 NOTIFICATION, W...c
-Assisted with PERIODIC GROUND CHECK AT 7-DAY INTERVALS CARRIED OUT IAW DIR 10317077 PT 000 VERS 01. SEE SAP REVISION 01315524 DCN 001, 002 AND 003 FOR DETAILS for Action Maintenance Notification 40152456 - D7 NOTIFICATION, WBC STORAGE 7 DAY PE- D7 NOTIFICATION, W...c</v>
+      <c r="I243" t="str">
+        <v>Assisted with PERIODIC GROUND CHECK AT 7-DAY INTERVALS CARRIED OUT IAW DIR 10317077 PT 000 VERS 01. SEE SAP REVISION 01315524 DCN 001, 002 AND 003 FOR DETAILS for Action Maintenance Notification 40152456 - D7 NOTIFICATION, WBC STORAGE 7 DAY PE- D7 NOTIFICATION, W...</v>
       </c>
       <c r="J243" t="str">
         <v>Kevin Cosgrave</v>

--- a/cap741-data.xlsx
+++ b/cap741-data.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -470,7 +470,7 @@
         <v>Dummy data test one</v>
       </c>
       <c r="I2" t="str">
-        <v>Dummy data test one</v>
+        <v>Dummy data test one Dummy data test oneDummy data test oneDummy data test oneDummy data test oneDummy data test oneDummy data test oneDummy data test oneDummy data test oneDummy data test oneDummy data test oneDummy data test  test oneDummy data test oneDummy data test oneDummy data test one fgfgfgfgggg</v>
       </c>
       <c r="J2" t="str">
         <v>Ioannis Orkos</v>
@@ -485,9 +485,50 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/cap741-data.xlsx
+++ b/cap741-data.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,10 +446,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>Airbus A350-1000 - RR Trent XWB-97</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>G-XWBA</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -485,57 +485,16 @@
         <v/>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v/>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C88"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -548,16 +507,973 @@
         <v>Aircraft Type</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>A350</v>
+      </c>
+      <c r="B2" t="str">
+        <v>G-XWBA</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Airbus A350-1000 - RR Trent XWB-97</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>A350</v>
+      </c>
+      <c r="B3" t="str">
+        <v>G-XWBC</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Airbus A350-1000 - RR Trent XWB-97</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>A350</v>
+      </c>
+      <c r="B4" t="str">
+        <v>G-XWBD</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Airbus A350-1000 - RR Trent XWB-97</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>A350</v>
+      </c>
+      <c r="B5" t="str">
+        <v>G-XWBE</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Airbus A350-1000 - RR Trent XWB-97</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>A350</v>
+      </c>
+      <c r="B6" t="str">
+        <v>G-XWBF</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Airbus A350-1000 - RR Trent XWB-97</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>A350</v>
+      </c>
+      <c r="B7" t="str">
+        <v>G-XWBG</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Airbus A350-1000 - RR Trent XWB-97</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>A350</v>
+      </c>
+      <c r="B8" t="str">
+        <v>G-XWBK</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Airbus A350-1000 - RR Trent XWB-97</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>A350</v>
+      </c>
+      <c r="B9" t="str">
+        <v>G-XWBM</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Airbus A350-1000 - RR Trent XWB-97</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>A350</v>
+      </c>
+      <c r="B10" t="str">
+        <v>G-XWBS</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Airbus A350-1000 - RR Trent XWB-97</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>A380</v>
+      </c>
+      <c r="B11" t="str">
+        <v>G-XLEB</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Airbus A380-800 - RR Trent 900</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>A380</v>
+      </c>
+      <c r="B12" t="str">
+        <v>G-XLEC</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Airbus A380-800 - RR Trent 900</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>A380</v>
+      </c>
+      <c r="B13" t="str">
+        <v>G-XLED</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Airbus A380-800 - RR Trent 900</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>A380</v>
+      </c>
+      <c r="B14" t="str">
+        <v>G-XLEE</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Airbus A380-800 - RR Trent 900</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>A380</v>
+      </c>
+      <c r="B15" t="str">
+        <v>G-XLEF</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Airbus A380-800 - RR Trent 900</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>A380</v>
+      </c>
+      <c r="B16" t="str">
+        <v>G-XLEG</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Airbus A380-800 - RR Trent 900</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>A380</v>
+      </c>
+      <c r="B17" t="str">
+        <v>G-XLEH</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Airbus A380-800 - RR Trent 900</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>A380</v>
+      </c>
+      <c r="B18" t="str">
+        <v>G-XLEI</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Airbus A380-800 - RR Trent 900</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>A380</v>
+      </c>
+      <c r="B19" t="str">
+        <v>G-XLEJ</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Airbus A380-800 - RR Trent 900</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>A380</v>
+      </c>
+      <c r="B20" t="str">
+        <v>G-XLEK</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Airbus A380-800 - RR Trent 900</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>A380</v>
+      </c>
+      <c r="B21" t="str">
+        <v>G-XLEL</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Airbus A380-800 - RR Trent 900</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B22" t="str">
+        <v>G-STBC</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B23" t="str">
+        <v>G-STBE</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B24" t="str">
+        <v>G-STBF</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B25" t="str">
+        <v>G-STBG</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B26" t="str">
+        <v>G-STBH</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B27" t="str">
+        <v>G-STBK</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B28" t="str">
+        <v>G-STBL</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B29" t="str">
+        <v>G-STBM</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B30" t="str">
+        <v>G-STBN</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B31" t="str">
+        <v>G-STBO</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B32" t="str">
+        <v>G-VIIA</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B33" t="str">
+        <v>G-VIIB</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B34" t="str">
+        <v>G-VIIC</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B35" t="str">
+        <v>G-VIIE</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B36" t="str">
+        <v>G-VIIF</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B37" t="str">
+        <v>G-VIIG</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B38" t="str">
+        <v>G-VIIH</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B39" t="str">
+        <v>G-VIIJ</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B40" t="str">
+        <v>G-VIIK</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B41" t="str">
+        <v>G-VIIL</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B42" t="str">
+        <v>G-VIIN</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B43" t="str">
+        <v>G-VIIP</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B44" t="str">
+        <v>G-VIIS</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B45" t="str">
+        <v>G-VIIV</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>B777 - GE90</v>
+      </c>
+      <c r="B46" t="str">
+        <v>G-VIIW</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Boeing 777-300ER - GE90</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>B777 - Trent 800</v>
+      </c>
+      <c r="B47" t="str">
+        <v>G-YMMB</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Boeing 777-200ER - RR Trent 800</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>B777 - Trent 800</v>
+      </c>
+      <c r="B48" t="str">
+        <v>G-YMMF</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Boeing 777-200ER - RR Trent 800</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>B777 - Trent 800</v>
+      </c>
+      <c r="B49" t="str">
+        <v>G-YMMG</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Boeing 777-200ER - RR Trent 800</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>B777 - Trent 800</v>
+      </c>
+      <c r="B50" t="str">
+        <v>G-YMMI</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Boeing 777-200ER - RR Trent 800</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>B777 - Trent 800</v>
+      </c>
+      <c r="B51" t="str">
+        <v>G-YMMJ</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Boeing 777-200ER - RR Trent 800</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>B777 - Trent 800</v>
+      </c>
+      <c r="B52" t="str">
+        <v>G-YMMK</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Boeing 777-200ER - RR Trent 800</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>B777 - Trent 800</v>
+      </c>
+      <c r="B53" t="str">
+        <v>G-YMMP</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Boeing 777-200ER - RR Trent 800</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>B777 - Trent 800</v>
+      </c>
+      <c r="B54" t="str">
+        <v>G-YMMT</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Boeing 777-200ER - RR Trent 800</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>B777 - Trent 800</v>
+      </c>
+      <c r="B55" t="str">
+        <v>G-YMMU</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Boeing 777-200ER - RR Trent 800</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B56" t="str">
+        <v>G-ZBJA</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Boeing 787-8 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B57" t="str">
+        <v>G-ZBJB</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Boeing 787-8 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B58" t="str">
+        <v>G-ZBJC</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Boeing 787-8 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B59" t="str">
+        <v>G-ZBJD</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Boeing 787-8 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B60" t="str">
+        <v>G-ZBJE</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Boeing 787-8 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B61" t="str">
+        <v>G-ZBJG</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Boeing 787-8 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B62" t="str">
+        <v>G-ZBJH</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Boeing 787-8 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B63" t="str">
+        <v>G-ZBJI</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Boeing 787-8 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B64" t="str">
+        <v>G-ZBJJ</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Boeing 787-8 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B65" t="str">
+        <v>G-ZBJK</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Boeing 787-8 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B66" t="str">
+        <v>G-ZBKA</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B67" t="str">
+        <v>G-ZBKB</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B68" t="str">
+        <v>G-ZBKC</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B69" t="str">
+        <v>G-ZBKD</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B70" t="str">
+        <v>G-ZBKE</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B71" t="str">
+        <v>G-ZBKF</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B72" t="str">
+        <v>G-ZBKH</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B73" t="str">
+        <v>G-ZBKI</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B74" t="str">
+        <v>G-ZBKJ</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B75" t="str">
+        <v>G-ZBKK</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B76" t="str">
+        <v>G-ZBKL</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B77" t="str">
+        <v>G-ZBKM</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B78" t="str">
+        <v>G-ZBKN</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B79" t="str">
+        <v>G-ZBKO</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B80" t="str">
+        <v>G-ZBKR</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B81" t="str">
+        <v>G-ZBKS</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Boeing 787-9 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B82" t="str">
+        <v>G-ZBLA</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Boeing 787-10 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B83" t="str">
+        <v>G-ZBLB</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Boeing 787-10 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B84" t="str">
+        <v>G-ZBLC</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Boeing 787-10 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B85" t="str">
+        <v>G-ZBLE</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Boeing 787-10 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B86" t="str">
+        <v>G-ZBLF</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Boeing 787-10 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B87" t="str">
+        <v>G-ZBLG</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Boeing 787-10 - RR Trent 1000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>B787</v>
+      </c>
+      <c r="B88" t="str">
+        <v>G-ZBLH</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Boeing 787-10 - RR Trent 1000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C88"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -567,9 +1483,657 @@
         <v>Description</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>00</v>
+      </c>
+      <c r="B2" t="str">
+        <v>General</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>01</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Maintenance Policy</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>02</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Operations</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>03</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Support</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>04</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Airworthiness Limitations</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>05</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Time Limits / Maintenance Checks</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>06</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Dimensions and Areas</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>07</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Lifting and Shoring</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>08</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Leveling and Weighing</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>09</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Towing and Taxiing</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>10</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Parking, Mooring, Storage and Return To Service</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>11</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Placards and Markings</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>12</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Servicing</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>13</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Hardware and General Tools</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Aircrew Information</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Change of Role</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>18</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Vibration and Noise Analysis</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>20</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Standard Practices - Airframe</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>21</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Air Conditioning and Pressurization</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>22</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Auto Flight</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>23</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Communications</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>24</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Electrical Power</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>25</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Equipment / Furnishings</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>26</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Fire Protection</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>27</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Flight Controls</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>28</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Fuel</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>29</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Hydraulic Power</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>30</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Ice and Rain Protection</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>31</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Indicating / Recording Systems</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>32</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Landing Gear</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>33</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Lights</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>34</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Navigation</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>35</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Oxygen</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>36</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Pneumatic</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>37</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Vacuum</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>38</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Water / Waste</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>39</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Electrical - Electronic Panels and Multipurpose Components</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>40</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Multisystem</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>41</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Water Ballast</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>42</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Integrated Modular Avionics (IMA)</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>43</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Emergency Solar Panel System (ESPS)</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>44</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Cabin Systems</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>45</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Central Maintenance / Onboard Maintenance Systems</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>46</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Information Systems</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>47</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Nitrogen Generation / Inert Gas System</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>48</v>
+      </c>
+      <c r="B47" t="str">
+        <v>In Flight Fuel Dispensing</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>49</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Airborne Auxiliary Power</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>50</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Cargo and Accessory Compartments</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>51</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Standard Practices and Structures - General</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>52</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Doors</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>53</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Fuselage</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>54</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Nacelles / Pylons</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>55</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Stabilizers</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>56</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Windows</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>57</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Wings</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>60</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Standard Practices - Prop./Rotor</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>61</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Propellers / Propulsion</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>62</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Main Rotor(s)</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>63</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Main Rotor Drive(s)</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>64</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Tail Rotor</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>65</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Tail Rotor Drive</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>66</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Folding Blades / Pylon</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>67</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Rotors Flight Control</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>70</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Standard Practices - Engine</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>71</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Power Plant</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>72</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Engine</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>73</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Engine - Fuel and Control</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>74</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Ignition</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>75</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Bleed Air</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>76</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Engine Controls</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>77</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Engine Indicating</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>78</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Exhaust</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>79</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Oil</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>80</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Starting</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>81</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Turbines (Reciprocating Engines)</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>82</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Water Injection</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>83</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Accessory Gear Box (Engine Driven)</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>84</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Propulsion Augmentation</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>85</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Reciprocating Engine</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>91</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Charts</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>97</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Image Recording</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B82"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/cap741-data.xlsx
+++ b/cap741-data.xlsx
@@ -7,7 +7,8 @@
     <sheet name="Aircraft" sheetId="2" r:id="rId2"/>
     <sheet name="Chapters" sheetId="3" r:id="rId3"/>
     <sheet name="Supervisors" sheetId="4" r:id="rId4"/>
-    <sheet name="Info" sheetId="5" r:id="rId5"/>
+    <sheet name="Flags" sheetId="5" r:id="rId5"/>
+    <sheet name="Info" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -401,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -432,15 +433,18 @@
         <v>Rewriten for cap741</v>
       </c>
       <c r="J1" t="str">
+        <v>Flags</v>
+      </c>
+      <c r="K1" t="str">
         <v>Approval Name</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Approval stamp</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Aprroval Licence No.</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Signed</v>
       </c>
     </row>
@@ -473,21 +477,24 @@
         <v>Dummy data test one Dummy data test oneDummy data test oneDummy data test oneDummy data test oneDummy data test oneDummy data test oneDummy data test oneDummy data test oneDummy data test oneDummy data test oneDummy data test  test oneDummy data test oneDummy data test oneDummy data test one fgfgfgfgggg</v>
       </c>
       <c r="J2" t="str">
-        <v>Ioannis Orkos</v>
+        <v>INSP - Inspections (Surveillance, Detailed &amp; General Visual); T/S - Troubleshooting</v>
       </c>
       <c r="K2" t="str">
         <v>Ioannis Orkos</v>
       </c>
       <c r="L2" t="str">
+        <v>Ioannis Orkos</v>
+      </c>
+      <c r="M2" t="str">
         <v>UK.XX.XXXXXXX</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2191,7 +2198,172 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C14"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Section</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Flag</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Color</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="B2" t="str">
+        <v>INSP - Inspections (Surveillance, Detailed &amp; General Visual)</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Gold</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="B3" t="str">
+        <v>T/S - Troubleshooting</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Purple</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="B4" t="str">
+        <v>F &amp; O - Functional &amp; Operational Check</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Green</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="B5" t="str">
+        <v>SRM - Structural Repair Manual</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Blue</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="B6" t="str">
+        <v>R &amp; I - Removal &amp; Installation</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Maroon</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>More</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Metal Damage Assessment*</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Black</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>More</v>
+      </c>
+      <c r="B8" t="str">
+        <v>CDCCL Tasks*</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Gray</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>More</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Metal Repair*</v>
+      </c>
+      <c r="C9" t="str">
+        <v>MistyRose</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>More</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Elect Wiring, Looming, Crimping, Soldering etc.*</v>
+      </c>
+      <c r="C10" t="str">
+        <v>SkyBlue</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>More</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Composite Damage Assessment*</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Teal</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>More</v>
+      </c>
+      <c r="B12" t="str">
+        <v>ESDS Procedures*</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Pink</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>More</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Composite Repair*</v>
+      </c>
+      <c r="C13" t="str">
+        <v>DarkRed</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>More</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Avionic LRU Replacement*</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Aqua</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2225,9 +2397,25 @@
         <v>User User</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Show Mind Map</v>
+      </c>
+      <c r="B5" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Page Grouping</v>
+      </c>
+      <c r="B6" t="str">
+        <v>type</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
   </ignoredErrors>
 </worksheet>
 </file>